--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484549_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484549_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.242000000000001</v>
+        <v>7.8381</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3672</v>
+        <v>6.1862</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8748</v>
+        <v>1.6519</v>
       </c>
       <c r="G2" t="n">
         <v>3.083</v>
@@ -610,13 +610,13 @@
         <v>3.1154</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3423</v>
+        <v>0.9384</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1584</v>
+        <v>0.9774</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1839</v>
+        <v>-0.0391</v>
       </c>
       <c r="V2" t="n">
         <v>2.5339</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2462</v>
+        <v>3.6454</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0698</v>
+        <v>1.0569</v>
       </c>
       <c r="F3" t="n">
-        <v>2.316</v>
+        <v>2.5885</v>
       </c>
       <c r="G3" t="n">
         <v>1.3037</v>
@@ -688,13 +688,13 @@
         <v>2.9321</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3952</v>
+        <v>0.004</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9366</v>
+        <v>0.1901</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4586</v>
+        <v>-0.1861</v>
       </c>
       <c r="V3" t="n">
         <v>0.3219</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1913</v>
+        <v>0.2679</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.5707</v>
+        <v>-2.1721</v>
       </c>
       <c r="F4" t="n">
-        <v>2.762</v>
+        <v>2.44</v>
       </c>
       <c r="G4" t="n">
         <v>0.1706</v>
@@ -766,13 +766,13 @@
         <v>3.1154</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8117</v>
+        <v>0.8882</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1984</v>
+        <v>0.5969</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6133</v>
+        <v>0.2913</v>
       </c>
       <c r="V4" t="n">
         <v>0.6751</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. MEDINA LERMA</t>
+          <t>A. CARRION BALLESTER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1781</v>
+        <v>0.2564</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5631</v>
+        <v>1.1386</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.385</v>
+        <v>-0.8822</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2874</v>
+        <v>0.6302</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2839</v>
+        <v>0.5885</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0035</v>
+        <v>0.0417</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4561</v>
+        <v>1.5247</v>
       </c>
       <c r="K5" t="n">
-        <v>0.331</v>
+        <v>2.1241</v>
       </c>
       <c r="L5" t="n">
-        <v>0.125</v>
+        <v>-0.5994</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7434</v>
+        <v>-0.8946</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6149</v>
+        <v>-1.5356</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1285</v>
+        <v>0.641</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3823</v>
+        <v>0.9163</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2664</v>
+        <v>-0.6461</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7014</v>
+        <v>-0.3861</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.435</v>
+        <v>-0.26</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.267</v>
+        <v>-0.6439</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.5889</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0549</v>
+        <v>0.1706</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1552</v>
+        <v>-0.004</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1003</v>
+        <v>0.1746</v>
       </c>
       <c r="G6" t="n">
         <v>0.1444</v>
@@ -922,13 +922,13 @@
         <v>0.3665</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2438</v>
+        <v>-0.0183</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2202</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0236</v>
+        <v>0.0507</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3219</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CARRION BALLESTER</t>
+          <t>R. MEDINA LERMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5108</v>
+        <v>-0.5163</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6439</v>
+        <v>0.6706</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.1547</v>
+        <v>-1.1868</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6302</v>
+        <v>-1.2874</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5885</v>
+        <v>-1.2839</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0417</v>
+        <v>-0.0035</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5247</v>
+        <v>0.4561</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1241</v>
+        <v>0.331</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5994</v>
+        <v>0.125</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8946</v>
+        <v>-1.7434</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5356</v>
+        <v>-1.6149</v>
       </c>
       <c r="O7" t="n">
-        <v>0.641</v>
+        <v>-0.1285</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9163</v>
+        <v>1.4661</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>2.3823</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4133</v>
+        <v>0.572</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8808</v>
+        <v>0.8088</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5325</v>
+        <v>-0.2368</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6439</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4611</v>
+        <v>-0.6502</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2792</v>
+        <v>0.9663</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7403</v>
+        <v>-1.6164</v>
       </c>
       <c r="G8" t="n">
         <v>0.1714</v>
@@ -1078,13 +1078,13 @@
         <v>1.2828</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0539</v>
+        <v>-0.243</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6976</v>
+        <v>-0.0105</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3563</v>
+        <v>-0.2325</v>
       </c>
       <c r="V8" t="n">
         <v>-0.945</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5674</v>
+        <v>-1.7542</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2409</v>
+        <v>-1.3781</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3265</v>
+        <v>-0.3761</v>
       </c>
       <c r="G9" t="n">
         <v>-3.2064</v>
@@ -1156,13 +1156,13 @@
         <v>2.7489</v>
       </c>
       <c r="S9" t="n">
-        <v>0.479</v>
+        <v>0.2922</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5837</v>
+        <v>0.4465</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1047</v>
+        <v>-0.1542</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5889</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1421</v>
+        <v>-2.1203</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6903</v>
+        <v>-0.5941</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4518</v>
+        <v>-1.5261</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3573</v>
@@ -1234,13 +1234,13 @@
         <v>0.1833</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.06759999999999999</v>
+        <v>-0.0458</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1652</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0975</v>
+        <v>0.0232</v>
       </c>
       <c r="V10" t="n">
         <v>-1.9005</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4424</v>
+        <v>-2.3575</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8619</v>
+        <v>-4.5044</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4195</v>
+        <v>2.147</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0096</v>
@@ -1312,13 +1312,13 @@
         <v>3.1154</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3681</v>
+        <v>0.4531</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2534</v>
+        <v>0.6109</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1147</v>
+        <v>-0.1578</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.678900000000001</v>
+        <v>4.7799</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2646000000000006</v>
+        <v>1.365899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>3.414299999999999</v>
+        <v>3.414399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3574</v>
@@ -1378,7 +1378,7 @@
         <v>-9.296500000000002</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8033</v>
+        <v>-0.8032999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>10.0792</v>
@@ -1390,10 +1390,10 @@
         <v>20.1584</v>
       </c>
       <c r="S12" t="n">
-        <v>1.0937</v>
+        <v>2.1947</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9949</v>
+        <v>3.096</v>
       </c>
       <c r="U12" t="n">
         <v>-0.9013</v>
@@ -1405,13 +1405,13 @@
         <v>2.6066</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.7429</v>
+        <v>-5.742900000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T. ROIG ARINO</t>
+          <t>P. FERRI BARCENAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.9716</v>
+        <v>5.7725</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8563</v>
+        <v>4.39</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1153</v>
+        <v>1.3825</v>
       </c>
       <c r="G13" t="n">
-        <v>1.6178</v>
+        <v>7.7989</v>
       </c>
       <c r="H13" t="n">
-        <v>2.102</v>
+        <v>5.2374</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4842</v>
+        <v>2.5615</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8091</v>
+        <v>7.0894</v>
       </c>
       <c r="K13" t="n">
-        <v>1.684</v>
+        <v>4.4958</v>
       </c>
       <c r="L13" t="n">
-        <v>0.125</v>
+        <v>2.5937</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1913</v>
+        <v>0.7095</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4179</v>
+        <v>0.7416</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6092</v>
+        <v>-0.0321</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9163</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R13" t="n">
-        <v>1.8326</v>
+        <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9036</v>
+        <v>0.0835</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6757</v>
+        <v>0.0494</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2279</v>
+        <v>0.0341</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5339</v>
+        <v>-0.6439</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2878</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.2461</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. FERRI BARCENAS</t>
+          <t>T. ROIG ARINO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3224</v>
+        <v>5.4587</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1015</v>
+        <v>2.3755</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2209</v>
+        <v>3.0831</v>
       </c>
       <c r="G14" t="n">
-        <v>7.7989</v>
+        <v>1.6178</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2374</v>
+        <v>2.102</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5615</v>
+        <v>-0.4842</v>
       </c>
       <c r="J14" t="n">
-        <v>7.0894</v>
+        <v>1.8091</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4958</v>
+        <v>1.684</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5937</v>
+        <v>0.125</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7095</v>
+        <v>-0.1913</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7416</v>
+        <v>0.4179</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0321</v>
+        <v>-0.6092</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.4661</v>
+        <v>0.9163</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2828</v>
+        <v>1.8326</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3666</v>
+        <v>0.3906</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2391</v>
+        <v>0.195</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1276</v>
+        <v>0.1957</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6439</v>
+        <v>2.5339</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.2878</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6439</v>
+        <v>1.2461</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9237</v>
+        <v>3.8816</v>
       </c>
       <c r="E15" t="n">
-        <v>5.5555</v>
+        <v>4.7863</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.6318</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>0.7373</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2022</v>
+        <v>0.1601</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0604</v>
+        <v>0.2911</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8582</v>
+        <v>-0.1311</v>
       </c>
       <c r="V15" t="n">
         <v>3.1674</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GARCIA SERRANO</t>
+          <t>J. DEL MORAL GALLARDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.0106</v>
+        <v>1.3435</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8235</v>
+        <v>-0.4856</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1871</v>
+        <v>1.8291</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3908</v>
+        <v>0.4526</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1792</v>
+        <v>0.5198</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2116</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7986</v>
+        <v>-0.0493</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7153</v>
+        <v>-0.1425</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0833</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.502</v>
       </c>
       <c r="N16" t="n">
-        <v>0.464</v>
+        <v>0.6623</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1282</v>
+        <v>-0.1603</v>
       </c>
       <c r="P16" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.2828</v>
+        <v>1.6493</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7307</v>
+        <v>-0.9433</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0249</v>
+        <v>-0.4363</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2942</v>
+        <v>-0.507</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.3937</v>
+        <v>0.1848</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.3937</v>
+        <v>0.1848</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. DEL MORAL GALLARDO</t>
+          <t>R. GARCIA SERRANO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6689000000000001</v>
+        <v>1.2661</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5817</v>
+        <v>1.0543</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2507</v>
+        <v>0.2119</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4526</v>
+        <v>1.3908</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5198</v>
+        <v>1.1792</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0.2116</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0493</v>
+        <v>0.7986</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1425</v>
+        <v>0.7153</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0833</v>
       </c>
       <c r="M17" t="n">
-        <v>0.502</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6623</v>
+        <v>0.464</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1603</v>
+        <v>0.1282</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6179</v>
+        <v>-0.0138</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5324</v>
+        <v>0.2557</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0855</v>
+        <v>-0.2694</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1848</v>
+        <v>-1.3937</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1848</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="18">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9141</v>
+        <v>-0.4449</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0649</v>
+        <v>-1.8726</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1509</v>
+        <v>1.4277</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6385</v>
@@ -2014,13 +2014,13 @@
         <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.4031</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3469</v>
+        <v>0.5392</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.413</v>
+        <v>-0.1361</v>
       </c>
       <c r="V20" t="n">
         <v>1.2566</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9491</v>
+        <v>-1.7188</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8774</v>
+        <v>-0.9736</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0717</v>
+        <v>-0.7453</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2396</v>
@@ -2092,13 +2092,13 @@
         <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2163</v>
+        <v>0.0139</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0905</v>
+        <v>-0.0056</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3068</v>
+        <v>0.0196</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7602</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3944</v>
+        <v>-2.125</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3809</v>
+        <v>-0.9962</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0135</v>
+        <v>-1.1287</v>
       </c>
       <c r="G22" t="n">
         <v>1.035</v>
@@ -2170,13 +2170,13 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0471</v>
+        <v>0.3165</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5143</v>
+        <v>-0.1297</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5614</v>
+        <v>0.4462</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2774</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5102</v>
+        <v>-2.4635</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2868</v>
+        <v>-2.1906</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2234</v>
+        <v>-0.2729</v>
       </c>
       <c r="G23" t="n">
         <v>-1.726</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1321</v>
+        <v>0.1787</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1101</v>
+        <v>-0.0139</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2422</v>
+        <v>0.1927</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.1016</v>
+        <v>-2.9764</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.387</v>
+        <v>-2.2908</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7147</v>
+        <v>-0.6855</v>
       </c>
       <c r="G24" t="n">
         <v>0.2337</v>
@@ -2326,13 +2326,13 @@
         <v>0.1833</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4294</v>
+        <v>0.5547</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3288</v>
+        <v>0.425</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1006</v>
+        <v>0.1297</v>
       </c>
       <c r="V24" t="n">
         <v>0.6335</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.3569</v>
+        <v>-3.6881</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.8885</v>
+        <v>-1.6</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4684</v>
+        <v>-2.0881</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9025</v>
@@ -2404,13 +2404,13 @@
         <v>0.1833</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5947</v>
+        <v>0.0741</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3122</v>
+        <v>-0.0237</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2824</v>
+        <v>0.0978</v>
       </c>
       <c r="V25" t="n">
         <v>-0.1267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.3003</v>
+        <v>-6.3708</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.2342</v>
+        <v>-6.5612</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.06610000000000001</v>
+        <v>0.1903</v>
       </c>
       <c r="G26" t="n">
         <v>-4.3523</v>
@@ -2482,13 +2482,13 @@
         <v>0.9163</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.6772</v>
+        <v>0.2523</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.9177999999999999</v>
+        <v>-0.2447</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2405</v>
+        <v>0.497</v>
       </c>
       <c r="V26" t="n">
         <v>-0.4382</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.679199999999997</v>
+        <v>-1.1149</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.414400000000001</v>
+        <v>-3.414300000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.2646999999999999</v>
+        <v>2.2994</v>
       </c>
       <c r="G27" t="n">
         <v>4.3574</v>
@@ -2539,7 +2539,7 @@
         <v>9.2964</v>
       </c>
       <c r="L27" t="n">
-        <v>0.8031000000000001</v>
+        <v>0.803100000000001</v>
       </c>
       <c r="M27" t="n">
         <v>-5.742000000000001</v>
@@ -2560,13 +2560,13 @@
         <v>10.0793</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.0937</v>
+        <v>1.4704</v>
       </c>
       <c r="T27" t="n">
-        <v>0.9013000000000004</v>
+        <v>0.9014999999999996</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.9951</v>
+        <v>0.5691999999999999</v>
       </c>
       <c r="V27" t="n">
         <v>3.136099999999999</v>
